--- a/ci1302_firmware/命令词播报词协议列表V3_履带车.xlsx
+++ b/ci1302_firmware/命令词播报词协议列表V3_履带车.xlsx
@@ -15,9 +15,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
   <si>
     <t/>
+  </si>
+  <si>
+    <t>瓦力来了，请吩咐</t>
+  </si>
+  <si>
+    <t>起床上班了喂</t>
+  </si>
+  <si>
+    <t>瓦力来了，别叫</t>
+  </si>
+  <si>
+    <t>行，我不动了</t>
+  </si>
+  <si>
+    <t>哈哈，我要开冲了</t>
+  </si>
+  <si>
+    <t>站住，你不要过来啊</t>
+  </si>
+  <si>
+    <t>知道了，已开启跟随功能</t>
+  </si>
+  <si>
+    <t>知道了，已关闭跟随功能</t>
+  </si>
+  <si>
+    <t>老子要开摆咯，别打扰我</t>
+  </si>
+  <si>
+    <t>瓦力来咯，别叫</t>
+  </si>
+  <si>
+    <t>起床上班咯</t>
+  </si>
+  <si>
+    <t>够大了不</t>
+  </si>
+  <si>
+    <t>够小了不</t>
+  </si>
+  <si>
+    <t>算球，我不动咯</t>
+  </si>
+  <si>
+    <t>哈哈，我要开冲咯</t>
+  </si>
+  <si>
+    <t>站住，你不要过来</t>
+  </si>
+  <si>
+    <t>晓得咯，已开启跟随功能</t>
   </si>
   <si>
     <r>
@@ -974,7 +1025,7 @@
   <cellStyleXfs>
     <xf numFmtId="300" fontId="6" fillId="5" borderId="5" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1016,6 +1067,12 @@
     </xf>
     <xf numFmtId="300" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="300" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -1317,40 +1374,40 @@
   <dimension ref="H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.29297" style="16" customWidth="1"/>
-    <col min="2" max="2" width="10.0898" style="16" customWidth="1"/>
-    <col min="3" max="3" width="31.3906" style="16" customWidth="1"/>
-    <col min="4" max="4" width="8.29297" style="16" customWidth="1"/>
-    <col min="5" max="5" width="19.082" style="16" customWidth="1"/>
-    <col min="6" max="6" width="8.29297" style="16" customWidth="1"/>
-    <col min="7" max="7" width="20.5625" style="16" customWidth="1"/>
-    <col min="8" max="8" width="20.4023" style="16" customWidth="1"/>
+    <col min="1" max="1" width="8.29297" style="18" customWidth="1"/>
+    <col min="2" max="2" width="10.0898" style="18" customWidth="1"/>
+    <col min="3" max="3" width="31.3906" style="18" customWidth="1"/>
+    <col min="4" max="4" width="8.29297" style="18" customWidth="1"/>
+    <col min="5" max="5" width="21.3398" style="18" customWidth="1"/>
+    <col min="6" max="6" width="8.29297" style="18" customWidth="1"/>
+    <col min="7" max="7" width="20.5625" style="18" customWidth="1"/>
+    <col min="8" max="8" width="20.4023" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1358,23 +1415,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C2" s="6" t="s"/>
       <c r="D2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>11</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1382,23 +1439,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C3" s="6" t="s"/>
       <c r="D3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>16</v>
+        <v>32</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>11</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1406,23 +1463,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C4" s="6" t="s"/>
       <c r="D4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>21</v>
+        <v>37</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1430,25 +1487,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>26</v>
+        <v>42</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1456,25 +1513,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="G6" s="6" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1482,35 +1539,35 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>14</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="9" t="s"/>
       <c r="B8" s="10" t="s"/>
       <c r="C8" s="11" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E8" s="11" t="s"/>
       <c r="F8" s="12" t="s"/>
@@ -1521,10 +1578,10 @@
       <c r="A9" s="9" t="s"/>
       <c r="B9" s="13" t="s"/>
       <c r="C9" s="11" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E9" s="11" t="s"/>
       <c r="F9" s="12" t="s"/>
@@ -1536,35 +1593,35 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>42</v>
+        <v>42</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>15</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="9" t="s"/>
       <c r="B11" s="10" t="s"/>
       <c r="C11" s="11" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E11" s="11" t="s"/>
       <c r="F11" s="12" t="s"/>
@@ -1575,10 +1632,10 @@
       <c r="A12" s="9" t="s"/>
       <c r="B12" s="13" t="s"/>
       <c r="C12" s="11" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E12" s="11" t="s"/>
       <c r="F12" s="12" t="s"/>
@@ -1590,35 +1647,35 @@
         <v>8</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="9" t="s"/>
       <c r="B14" s="10" t="s"/>
       <c r="C14" s="11" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E14" s="11" t="s"/>
       <c r="F14" s="12" t="s"/>
@@ -1629,10 +1686,10 @@
       <c r="A15" s="9" t="s"/>
       <c r="B15" s="13" t="s"/>
       <c r="C15" s="11" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E15" s="11" t="s"/>
       <c r="F15" s="12" t="s"/>
@@ -1644,35 +1701,35 @@
         <v>9</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="9" t="s"/>
       <c r="B17" s="10" t="s"/>
       <c r="C17" s="11" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E17" s="11" t="s"/>
       <c r="F17" s="12" t="s"/>
@@ -1683,10 +1740,10 @@
       <c r="A18" s="9" t="s"/>
       <c r="B18" s="13" t="s"/>
       <c r="C18" s="11" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E18" s="11" t="s"/>
       <c r="F18" s="12" t="s"/>
@@ -1698,35 +1755,35 @@
         <v>10</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="9" t="s"/>
       <c r="B20" s="10" t="s"/>
       <c r="C20" s="11" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E20" s="11" t="s"/>
       <c r="F20" s="12" t="s"/>
@@ -1737,10 +1794,10 @@
       <c r="A21" s="9" t="s"/>
       <c r="B21" s="13" t="s"/>
       <c r="C21" s="11" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E21" s="11" t="s"/>
       <c r="F21" s="12" t="s"/>
@@ -1752,35 +1809,35 @@
         <v>11</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="9" t="s"/>
       <c r="B23" s="10" t="s"/>
       <c r="C23" s="11" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E23" s="11" t="s"/>
       <c r="F23" s="12" t="s"/>
@@ -1791,10 +1848,10 @@
       <c r="A24" s="9" t="s"/>
       <c r="B24" s="13" t="s"/>
       <c r="C24" s="11" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E24" s="11" t="s"/>
       <c r="F24" s="12" t="s"/>
@@ -1806,35 +1863,35 @@
         <v>12</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="9" t="s"/>
       <c r="B26" s="10" t="s"/>
       <c r="C26" s="11" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E26" s="11" t="s"/>
       <c r="F26" s="12" t="s"/>
@@ -1845,10 +1902,10 @@
       <c r="A27" s="9" t="s"/>
       <c r="B27" s="13" t="s"/>
       <c r="C27" s="11" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E27" s="11" t="s"/>
       <c r="F27" s="12" t="s"/>
@@ -1860,35 +1917,35 @@
         <v>13</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>84</v>
+        <v>42</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>17</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="9" t="s"/>
       <c r="B29" s="10" t="s"/>
       <c r="C29" s="11" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E29" s="11" t="s"/>
       <c r="F29" s="12" t="s"/>
@@ -1899,10 +1956,10 @@
       <c r="A30" s="9" t="s"/>
       <c r="B30" s="10" t="s"/>
       <c r="C30" s="11" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E30" s="11" t="s"/>
       <c r="F30" s="12" t="s"/>
@@ -1913,10 +1970,10 @@
       <c r="A31" s="9" t="s"/>
       <c r="B31" s="13" t="s"/>
       <c r="C31" s="11" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E31" s="11" t="s"/>
       <c r="F31" s="12" t="s"/>
@@ -1928,35 +1985,35 @@
         <v>14</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>92</v>
+        <v>42</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="9" t="s"/>
       <c r="B33" s="10" t="s"/>
       <c r="C33" s="11" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E33" s="11" t="s"/>
       <c r="F33" s="12" t="s"/>
@@ -1967,10 +2024,10 @@
       <c r="A34" s="9" t="s"/>
       <c r="B34" s="10" t="s"/>
       <c r="C34" s="11" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E34" s="11" t="s"/>
       <c r="F34" s="12" t="s"/>
@@ -1981,10 +2038,10 @@
       <c r="A35" s="9" t="s"/>
       <c r="B35" s="13" t="s"/>
       <c r="C35" s="11" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E35" s="11" t="s"/>
       <c r="F35" s="12" t="s"/>
@@ -2005,12 +2062,12 @@
   <dimension ref="A81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="90" style="16" customWidth="1"/>
+    <col min="1" max="1" width="90" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="14" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -2018,12 +2075,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="14" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="15" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -2031,22 +2088,22 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="14" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="15" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="15" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="15" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -2054,17 +2111,17 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="14" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="15" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="15" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -2072,12 +2129,12 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="14" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="15" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -2085,47 +2142,47 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="15" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="15" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="15" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="15" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="15" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="15" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="15" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="15" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="15" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -2133,37 +2190,37 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="14" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="15" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="15" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="15" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="15" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="15" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="15" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -2171,32 +2228,32 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="15" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="15" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="15" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="15" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="15" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -2204,27 +2261,27 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="14" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="15" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="15" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="15" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="15" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -2232,17 +2289,17 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="14" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="15" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="15" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -2250,37 +2307,37 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="14" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="15" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="15" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="15" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="15" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="15" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="15" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -2288,77 +2345,77 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="14" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="15" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="15" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="15" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="15" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="15" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="15" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="15" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="15" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="15" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="15" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="15" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="15" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="15" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="15" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -2366,27 +2423,27 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="14" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="15" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="15" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="15" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="15" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/ci1302_firmware/命令词播报词协议列表V3_履带车.xlsx
+++ b/ci1302_firmware/命令词播报词协议列表V3_履带车.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
   <si>
     <t/>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>晓得咯，已开启跟随功能</t>
+  </si>
+  <si>
+    <t>晓得咯，已关闭跟随功能</t>
   </si>
   <si>
     <r>
@@ -1386,28 +1389,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1415,23 +1418,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="6" t="s"/>
       <c r="D2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="16" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1439,23 +1442,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="6" t="s"/>
       <c r="D3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1463,23 +1466,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="6" t="s"/>
       <c r="D4" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1487,25 +1490,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1513,25 +1516,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1539,35 +1542,35 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="9" t="s"/>
       <c r="B8" s="10" t="s"/>
       <c r="C8" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" s="11" t="s"/>
       <c r="F8" s="12" t="s"/>
@@ -1578,10 +1581,10 @@
       <c r="A9" s="9" t="s"/>
       <c r="B9" s="13" t="s"/>
       <c r="C9" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="11" t="s"/>
       <c r="F9" s="12" t="s"/>
@@ -1593,35 +1596,35 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="9" t="s"/>
       <c r="B11" s="10" t="s"/>
       <c r="C11" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" s="11" t="s"/>
       <c r="F11" s="12" t="s"/>
@@ -1632,10 +1635,10 @@
       <c r="A12" s="9" t="s"/>
       <c r="B12" s="13" t="s"/>
       <c r="C12" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" s="11" t="s"/>
       <c r="F12" s="12" t="s"/>
@@ -1647,35 +1650,35 @@
         <v>8</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="9" t="s"/>
       <c r="B14" s="10" t="s"/>
       <c r="C14" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E14" s="11" t="s"/>
       <c r="F14" s="12" t="s"/>
@@ -1686,10 +1689,10 @@
       <c r="A15" s="9" t="s"/>
       <c r="B15" s="13" t="s"/>
       <c r="C15" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" s="11" t="s"/>
       <c r="F15" s="12" t="s"/>
@@ -1701,35 +1704,35 @@
         <v>9</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="9" t="s"/>
       <c r="B17" s="10" t="s"/>
       <c r="C17" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" s="11" t="s"/>
       <c r="F17" s="12" t="s"/>
@@ -1740,10 +1743,10 @@
       <c r="A18" s="9" t="s"/>
       <c r="B18" s="13" t="s"/>
       <c r="C18" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" s="11" t="s"/>
       <c r="F18" s="12" t="s"/>
@@ -1755,35 +1758,35 @@
         <v>10</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="9" t="s"/>
       <c r="B20" s="10" t="s"/>
       <c r="C20" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" s="11" t="s"/>
       <c r="F20" s="12" t="s"/>
@@ -1794,10 +1797,10 @@
       <c r="A21" s="9" t="s"/>
       <c r="B21" s="13" t="s"/>
       <c r="C21" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21" s="11" t="s"/>
       <c r="F21" s="12" t="s"/>
@@ -1809,35 +1812,35 @@
         <v>11</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="9" t="s"/>
       <c r="B23" s="10" t="s"/>
       <c r="C23" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23" s="11" t="s"/>
       <c r="F23" s="12" t="s"/>
@@ -1848,10 +1851,10 @@
       <c r="A24" s="9" t="s"/>
       <c r="B24" s="13" t="s"/>
       <c r="C24" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E24" s="11" t="s"/>
       <c r="F24" s="12" t="s"/>
@@ -1863,35 +1866,35 @@
         <v>12</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="9" t="s"/>
       <c r="B26" s="10" t="s"/>
       <c r="C26" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E26" s="11" t="s"/>
       <c r="F26" s="12" t="s"/>
@@ -1902,10 +1905,10 @@
       <c r="A27" s="9" t="s"/>
       <c r="B27" s="13" t="s"/>
       <c r="C27" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E27" s="11" t="s"/>
       <c r="F27" s="12" t="s"/>
@@ -1917,35 +1920,35 @@
         <v>13</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="9" t="s"/>
       <c r="B29" s="10" t="s"/>
       <c r="C29" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E29" s="11" t="s"/>
       <c r="F29" s="12" t="s"/>
@@ -1956,10 +1959,10 @@
       <c r="A30" s="9" t="s"/>
       <c r="B30" s="10" t="s"/>
       <c r="C30" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E30" s="11" t="s"/>
       <c r="F30" s="12" t="s"/>
@@ -1970,10 +1973,10 @@
       <c r="A31" s="9" t="s"/>
       <c r="B31" s="13" t="s"/>
       <c r="C31" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E31" s="11" t="s"/>
       <c r="F31" s="12" t="s"/>
@@ -1985,35 +1988,35 @@
         <v>14</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="9" t="s"/>
       <c r="B33" s="10" t="s"/>
       <c r="C33" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E33" s="11" t="s"/>
       <c r="F33" s="12" t="s"/>
@@ -2024,10 +2027,10 @@
       <c r="A34" s="9" t="s"/>
       <c r="B34" s="10" t="s"/>
       <c r="C34" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E34" s="11" t="s"/>
       <c r="F34" s="12" t="s"/>
@@ -2038,10 +2041,10 @@
       <c r="A35" s="9" t="s"/>
       <c r="B35" s="13" t="s"/>
       <c r="C35" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E35" s="11" t="s"/>
       <c r="F35" s="12" t="s"/>
@@ -2067,7 +2070,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -2075,12 +2078,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -2088,22 +2091,22 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -2111,17 +2114,17 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -2129,12 +2132,12 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -2142,47 +2145,47 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -2190,37 +2193,37 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -2228,32 +2231,32 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -2261,27 +2264,27 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -2289,17 +2292,17 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -2307,37 +2310,37 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -2345,77 +2348,77 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -2423,27 +2426,27 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
